--- a/data/sdsa/raw/r_g_historic_data.xlsx
+++ b/data/sdsa/raw/r_g_historic_data.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10608"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="11130"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/danpost/random_bernstein/debt_sustainability/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/danpost/debt_sustainability_project/data/sdsa/raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4050FDB5-867A-3642-BAF0-3D7B71AAD382}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9B0578D-8AA0-304E-91E2-6DC5302CF935}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17340" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="67">
   <si>
     <r>
       <rPr>
@@ -251,6 +251,18 @@
   </si>
   <si>
     <t>interest payment (billions)</t>
+  </si>
+  <si>
+    <t>total outlays (pct of GDP)</t>
+  </si>
+  <si>
+    <t>net interest (pct of GDP)</t>
+  </si>
+  <si>
+    <t>total revenues (pct of GDP)</t>
+  </si>
+  <si>
+    <t>primary balance (pct of GDP)</t>
   </si>
 </sst>
 </file>
@@ -999,6 +1011,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -1006,7 +1019,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -1927,16 +1939,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE499878-7922-1B4F-8166-A11896EE1562}">
-  <dimension ref="A1:F64"/>
+  <dimension ref="A1:J64"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="17.1640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="23" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="17" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="19.5" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="19.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>60</v>
       </c>
@@ -1955,8 +1967,20 @@
       <c r="F1" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G1" t="s">
+        <v>63</v>
+      </c>
+      <c r="H1" t="s">
+        <v>64</v>
+      </c>
+      <c r="I1" t="s">
+        <v>65</v>
+      </c>
+      <c r="J1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2" s="1">
         <v>1962</v>
       </c>
@@ -1977,8 +2001,21 @@
         <f>B2 + D2</f>
         <v>-0.24499999999999922</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G2" s="5">
+        <v>18.239000000000001</v>
+      </c>
+      <c r="H2" s="5">
+        <v>1.1759999999999999</v>
+      </c>
+      <c r="I2" s="5">
+        <v>17.018999999999998</v>
+      </c>
+      <c r="J2" s="14">
+        <f>(I2-G2) + H2</f>
+        <v>-4.4000000000002482E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A3" s="1">
         <v>1963</v>
       </c>
@@ -1999,8 +2036,21 @@
         <f t="shared" ref="F3:F64" si="1">B3 + D3</f>
         <v>2.944</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G3" s="5">
+        <v>18.006</v>
+      </c>
+      <c r="H3" s="5">
+        <v>1.252</v>
+      </c>
+      <c r="I3" s="5">
+        <v>17.236999999999998</v>
+      </c>
+      <c r="J3" s="14">
+        <f t="shared" ref="J3:J64" si="2">(I3-G3) + H3</f>
+        <v>0.4829999999999981</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
         <v>1964</v>
       </c>
@@ -2021,8 +2071,21 @@
         <f t="shared" si="1"/>
         <v>2.2849999999999993</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G4" s="5">
+        <v>17.913</v>
+      </c>
+      <c r="H4" s="5">
+        <v>1.2390000000000001</v>
+      </c>
+      <c r="I4" s="5">
+        <v>17.018999999999998</v>
+      </c>
+      <c r="J4" s="14">
+        <f t="shared" si="2"/>
+        <v>0.3449999999999982</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
         <v>1965</v>
       </c>
@@ -2043,8 +2106,21 @@
         <f t="shared" si="1"/>
         <v>7.1879999999999997</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G5" s="5">
+        <v>16.667999999999999</v>
+      </c>
+      <c r="H5" s="5">
+        <v>1.2110000000000001</v>
+      </c>
+      <c r="I5" s="5">
+        <v>16.469000000000001</v>
+      </c>
+      <c r="J5" s="14">
+        <f t="shared" si="2"/>
+        <v>1.012000000000002</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
         <v>1966</v>
       </c>
@@ -2065,8 +2141,21 @@
         <f t="shared" si="1"/>
         <v>5.7040000000000006</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G6" s="5">
+        <v>17.236999999999998</v>
+      </c>
+      <c r="H6" s="5">
+        <v>1.2030000000000001</v>
+      </c>
+      <c r="I6" s="5">
+        <v>16.763999999999999</v>
+      </c>
+      <c r="J6" s="14">
+        <f t="shared" si="2"/>
+        <v>0.73000000000000109</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
         <v>1967</v>
       </c>
@@ -2087,8 +2176,21 @@
         <f t="shared" si="1"/>
         <v>1.6580000000000013</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G7" s="5">
+        <v>18.824000000000002</v>
+      </c>
+      <c r="H7" s="5">
+        <v>1.2270000000000001</v>
+      </c>
+      <c r="I7" s="5">
+        <v>17.791</v>
+      </c>
+      <c r="J7" s="14">
+        <f t="shared" si="2"/>
+        <v>0.19399999999999884</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A8" s="1">
         <v>1968</v>
       </c>
@@ -2109,8 +2211,21 @@
         <f t="shared" si="1"/>
         <v>-14.061000000000002</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G8" s="5">
+        <v>19.846</v>
+      </c>
+      <c r="H8" s="5">
+        <v>1.236</v>
+      </c>
+      <c r="I8" s="5">
+        <v>17.042999999999999</v>
+      </c>
+      <c r="J8" s="14">
+        <f t="shared" si="2"/>
+        <v>-1.5670000000000008</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9" s="1">
         <v>1969</v>
       </c>
@@ -2131,8 +2246,21 @@
         <f t="shared" si="1"/>
         <v>15.943</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G9" s="5">
+        <v>18.733000000000001</v>
+      </c>
+      <c r="H9" s="5">
+        <v>1.2949999999999999</v>
+      </c>
+      <c r="I9" s="5">
+        <v>19.064</v>
+      </c>
+      <c r="J9" s="14">
+        <f t="shared" si="2"/>
+        <v>1.6259999999999994</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A10" s="1">
         <v>1970</v>
       </c>
@@ -2153,8 +2281,21 @@
         <f t="shared" si="1"/>
         <v>11.558</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G10" s="5">
+        <v>18.692</v>
+      </c>
+      <c r="H10" s="5">
+        <v>1.3740000000000001</v>
+      </c>
+      <c r="I10" s="5">
+        <v>18.420999999999999</v>
+      </c>
+      <c r="J10" s="14">
+        <f t="shared" si="2"/>
+        <v>1.1029999999999993</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A11" s="1">
         <v>1971</v>
       </c>
@@ -2175,8 +2316,21 @@
         <f t="shared" si="1"/>
         <v>-8.2330000000000005</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G11" s="5">
+        <v>18.823</v>
+      </c>
+      <c r="H11" s="5">
+        <v>1.329</v>
+      </c>
+      <c r="I11" s="5">
+        <v>16.760000000000002</v>
+      </c>
+      <c r="J11" s="14">
+        <f t="shared" si="2"/>
+        <v>-0.73399999999999888</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A12" s="1">
         <v>1972</v>
       </c>
@@ -2197,8 +2351,21 @@
         <f t="shared" si="1"/>
         <v>-7.8730000000000011</v>
       </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G12" s="5">
+        <v>18.966999999999999</v>
+      </c>
+      <c r="H12" s="5">
+        <v>1.2729999999999999</v>
+      </c>
+      <c r="I12" s="5">
+        <v>17.045000000000002</v>
+      </c>
+      <c r="J12" s="14">
+        <f t="shared" si="2"/>
+        <v>-0.64899999999999713</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A13" s="1">
         <v>1973</v>
       </c>
@@ -2219,8 +2386,21 @@
         <f t="shared" si="1"/>
         <v>2.391</v>
       </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G13" s="5">
+        <v>18.164000000000001</v>
+      </c>
+      <c r="H13" s="5">
+        <v>1.2829999999999999</v>
+      </c>
+      <c r="I13" s="5">
+        <v>17.062000000000001</v>
+      </c>
+      <c r="J13" s="14">
+        <f t="shared" si="2"/>
+        <v>0.18099999999999961</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A14" s="1">
         <v>1974</v>
       </c>
@@ -2241,8 +2421,21 @@
         <f t="shared" si="1"/>
         <v>15.264999999999999</v>
       </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G14" s="5">
+        <v>18.164999999999999</v>
+      </c>
+      <c r="H14" s="5">
+        <v>1.446</v>
+      </c>
+      <c r="I14" s="5">
+        <v>17.751000000000001</v>
+      </c>
+      <c r="J14" s="14">
+        <f t="shared" si="2"/>
+        <v>1.032000000000002</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A15" s="1">
         <v>1975</v>
       </c>
@@ -2263,8 +2456,21 @@
         <f t="shared" si="1"/>
         <v>-30.041</v>
       </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G15" s="5">
+        <v>20.681000000000001</v>
+      </c>
+      <c r="H15" s="5">
+        <v>1.446</v>
+      </c>
+      <c r="I15" s="5">
+        <v>17.367999999999999</v>
+      </c>
+      <c r="J15" s="14">
+        <f t="shared" si="2"/>
+        <v>-1.8670000000000024</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A16" s="1">
         <v>1976</v>
       </c>
@@ -2285,8 +2491,21 @@
         <f t="shared" si="1"/>
         <v>-47.031999999999996</v>
       </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G16" s="5">
+        <v>20.815999999999999</v>
+      </c>
+      <c r="H16" s="5">
+        <v>1.496</v>
+      </c>
+      <c r="I16" s="5">
+        <v>16.687999999999999</v>
+      </c>
+      <c r="J16" s="14">
+        <f t="shared" si="2"/>
+        <v>-2.6320000000000001</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A17" s="1">
         <v>1977</v>
       </c>
@@ -2307,8 +2526,21 @@
         <f t="shared" si="1"/>
         <v>-23.759</v>
       </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G17" s="5">
+        <v>20.215</v>
+      </c>
+      <c r="H17" s="5">
+        <v>1.4770000000000001</v>
+      </c>
+      <c r="I17" s="5">
+        <v>17.564</v>
+      </c>
+      <c r="J17" s="14">
+        <f t="shared" si="2"/>
+        <v>-1.1739999999999997</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A18" s="1">
         <v>1978</v>
       </c>
@@ -2329,8 +2561,21 @@
         <f t="shared" si="1"/>
         <v>-23.685000000000002</v>
       </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G18" s="5">
+        <v>20.178000000000001</v>
+      </c>
+      <c r="H18" s="5">
+        <v>1.56</v>
+      </c>
+      <c r="I18" s="5">
+        <v>17.574999999999999</v>
+      </c>
+      <c r="J18" s="14">
+        <f t="shared" si="2"/>
+        <v>-1.0430000000000015</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A19" s="1">
         <v>1979</v>
       </c>
@@ -2351,8 +2596,21 @@
         <f t="shared" si="1"/>
         <v>1.8730000000000047</v>
       </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G19" s="5">
+        <v>19.646000000000001</v>
+      </c>
+      <c r="H19" s="5">
+        <v>1.6619999999999999</v>
+      </c>
+      <c r="I19" s="5">
+        <v>18.058</v>
+      </c>
+      <c r="J19" s="14">
+        <f t="shared" si="2"/>
+        <v>7.3999999999998956E-2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A20" s="1">
         <v>1980</v>
       </c>
@@ -2373,8 +2631,21 @@
         <f t="shared" si="1"/>
         <v>-21.328999999999994</v>
       </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G20" s="5">
+        <v>21.166</v>
+      </c>
+      <c r="H20" s="5">
+        <v>1.8819999999999999</v>
+      </c>
+      <c r="I20" s="5">
+        <v>18.521999999999998</v>
+      </c>
+      <c r="J20" s="14">
+        <f t="shared" si="2"/>
+        <v>-0.76200000000000201</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A21" s="1">
         <v>1981</v>
       </c>
@@ -2395,8 +2666,21 @@
         <f t="shared" si="1"/>
         <v>-10.168999999999997</v>
       </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G21" s="5">
+        <v>21.646999999999998</v>
+      </c>
+      <c r="H21" s="5">
+        <v>2.1949999999999998</v>
+      </c>
+      <c r="I21" s="5">
+        <v>19.126000000000001</v>
+      </c>
+      <c r="J21" s="14">
+        <f t="shared" si="2"/>
+        <v>-0.3259999999999974</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A22" s="1">
         <v>1982</v>
       </c>
@@ -2417,8 +2701,21 @@
         <f t="shared" si="1"/>
         <v>-42.977000000000004</v>
       </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G22" s="5">
+        <v>22.507000000000001</v>
+      </c>
+      <c r="H22" s="5">
+        <v>2.5659999999999998</v>
+      </c>
+      <c r="I22" s="5">
+        <v>18.645</v>
+      </c>
+      <c r="J22" s="14">
+        <f t="shared" si="2"/>
+        <v>-1.296000000000002</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A23" s="1">
         <v>1983</v>
       </c>
@@ -2439,8 +2736,21 @@
         <f t="shared" si="1"/>
         <v>-118.003</v>
       </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G23" s="5">
+        <v>22.861000000000001</v>
+      </c>
+      <c r="H23" s="5">
+        <v>2.54</v>
+      </c>
+      <c r="I23" s="5">
+        <v>16.984000000000002</v>
+      </c>
+      <c r="J23" s="14">
+        <f t="shared" si="2"/>
+        <v>-3.3369999999999989</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A24" s="1">
         <v>1984</v>
       </c>
@@ -2461,8 +2771,21 @@
         <f t="shared" si="1"/>
         <v>-74.268000000000001</v>
       </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G24" s="5">
+        <v>21.568999999999999</v>
+      </c>
+      <c r="H24" s="5">
+        <v>2.8130000000000002</v>
+      </c>
+      <c r="I24" s="5">
+        <v>16.875</v>
+      </c>
+      <c r="J24" s="14">
+        <f t="shared" si="2"/>
+        <v>-1.8809999999999989</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A25" s="1">
         <v>1985</v>
       </c>
@@ -2483,8 +2806,21 @@
         <f t="shared" si="1"/>
         <v>-82.806999999999988</v>
       </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G25" s="5">
+        <v>22.187999999999999</v>
+      </c>
+      <c r="H25" s="5">
+        <v>3.036</v>
+      </c>
+      <c r="I25" s="5">
+        <v>17.21</v>
+      </c>
+      <c r="J25" s="14">
+        <f t="shared" si="2"/>
+        <v>-1.941999999999998</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A26" s="1">
         <v>1986</v>
       </c>
@@ -2505,8 +2841,21 @@
         <f t="shared" si="1"/>
         <v>-85.227000000000004</v>
       </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G26" s="5">
+        <v>21.881</v>
+      </c>
+      <c r="H26" s="5">
+        <v>3.0049999999999999</v>
+      </c>
+      <c r="I26" s="5">
+        <v>16.992999999999999</v>
+      </c>
+      <c r="J26" s="14">
+        <f t="shared" si="2"/>
+        <v>-1.8830000000000018</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A27" s="1">
         <v>1987</v>
       </c>
@@ -2527,8 +2876,21 @@
         <f t="shared" si="1"/>
         <v>-11.129999999999995</v>
       </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G27" s="5">
+        <v>21.059000000000001</v>
+      </c>
+      <c r="H27" s="5">
+        <v>2.907</v>
+      </c>
+      <c r="I27" s="5">
+        <v>17.917999999999999</v>
+      </c>
+      <c r="J27" s="14">
+        <f t="shared" si="2"/>
+        <v>-0.23400000000000176</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A28" s="1">
         <v>1988</v>
       </c>
@@ -2549,8 +2911,21 @@
         <f t="shared" si="1"/>
         <v>-3.3769999999999811</v>
       </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G28" s="5">
+        <v>20.713999999999999</v>
+      </c>
+      <c r="H28" s="5">
+        <v>2.9540000000000002</v>
+      </c>
+      <c r="I28" s="5">
+        <v>17.693999999999999</v>
+      </c>
+      <c r="J28" s="14">
+        <f t="shared" si="2"/>
+        <v>-6.5999999999999392E-2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A29" s="1">
         <v>1989</v>
       </c>
@@ -2571,8 +2946,21 @@
         <f t="shared" si="1"/>
         <v>16.36099999999999</v>
       </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G29" s="5">
+        <v>20.591000000000001</v>
+      </c>
+      <c r="H29" s="5">
+        <v>3.0419999999999998</v>
+      </c>
+      <c r="I29" s="5">
+        <v>17.843</v>
+      </c>
+      <c r="J29" s="14">
+        <f t="shared" si="2"/>
+        <v>0.29399999999999871</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A30" s="1">
         <v>1990</v>
       </c>
@@ -2593,8 +2981,21 @@
         <f t="shared" si="1"/>
         <v>-36.734999999999985</v>
       </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G30" s="5">
+        <v>21.242000000000001</v>
+      </c>
+      <c r="H30" s="5">
+        <v>3.125</v>
+      </c>
+      <c r="I30" s="5">
+        <v>17.495000000000001</v>
+      </c>
+      <c r="J30" s="14">
+        <f t="shared" si="2"/>
+        <v>-0.62199999999999989</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A31" s="1">
         <v>1991</v>
       </c>
@@ -2615,8 +3016,21 @@
         <f t="shared" si="1"/>
         <v>-74.837000000000018</v>
       </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G31" s="5">
+        <v>21.733000000000001</v>
+      </c>
+      <c r="H31" s="5">
+        <v>3.1909999999999998</v>
+      </c>
+      <c r="I31" s="5">
+        <v>17.314</v>
+      </c>
+      <c r="J31" s="14">
+        <f t="shared" si="2"/>
+        <v>-1.2280000000000006</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A32" s="1">
         <v>1992</v>
       </c>
@@ -2637,8 +3051,21 @@
         <f t="shared" si="1"/>
         <v>-91.021999999999991</v>
       </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G32" s="5">
+        <v>21.532</v>
+      </c>
+      <c r="H32" s="5">
+        <v>3.1070000000000002</v>
+      </c>
+      <c r="I32" s="5">
+        <v>17.007000000000001</v>
+      </c>
+      <c r="J32" s="14">
+        <f t="shared" si="2"/>
+        <v>-1.4179999999999984</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A33" s="1">
         <v>1993</v>
       </c>
@@ -2659,8 +3086,21 @@
         <f t="shared" si="1"/>
         <v>-56.350999999999999</v>
       </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G33" s="5">
+        <v>20.802</v>
+      </c>
+      <c r="H33" s="5">
+        <v>2.9329999999999998</v>
+      </c>
+      <c r="I33" s="5">
+        <v>17.036999999999999</v>
+      </c>
+      <c r="J33" s="14">
+        <f t="shared" si="2"/>
+        <v>-0.83200000000000074</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A34" s="1">
         <v>1994</v>
       </c>
@@ -2681,8 +3121,21 @@
         <f t="shared" si="1"/>
         <v>-0.28600000000000136</v>
       </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G34" s="5">
+        <v>20.367999999999999</v>
+      </c>
+      <c r="H34" s="5">
+        <v>2.8279999999999998</v>
+      </c>
+      <c r="I34" s="5">
+        <v>17.536000000000001</v>
+      </c>
+      <c r="J34" s="14">
+        <f t="shared" si="2"/>
+        <v>-3.999999999997339E-3</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A35" s="1">
         <v>1995</v>
       </c>
@@ -2703,8 +3156,21 @@
         <f t="shared" si="1"/>
         <v>68.147999999999996</v>
       </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G35" s="5">
+        <v>20.047999999999998</v>
+      </c>
+      <c r="H35" s="5">
+        <v>3.07</v>
+      </c>
+      <c r="I35" s="5">
+        <v>17.88</v>
+      </c>
+      <c r="J35" s="14">
+        <f t="shared" si="2"/>
+        <v>0.90200000000000058</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A36" s="1">
         <v>1996</v>
       </c>
@@ -2725,8 +3191,21 @@
         <f t="shared" si="1"/>
         <v>133.66899999999998</v>
       </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G36" s="5">
+        <v>19.625</v>
+      </c>
+      <c r="H36" s="5">
+        <v>3.032</v>
+      </c>
+      <c r="I36" s="5">
+        <v>18.274000000000001</v>
+      </c>
+      <c r="J36" s="14">
+        <f t="shared" si="2"/>
+        <v>1.6810000000000009</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A37" s="1">
         <v>1997</v>
       </c>
@@ -2747,8 +3226,21 @@
         <f t="shared" si="1"/>
         <v>222.11599999999999</v>
       </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G37" s="5">
+        <v>18.946000000000002</v>
+      </c>
+      <c r="H37" s="5">
+        <v>2.887</v>
+      </c>
+      <c r="I37" s="5">
+        <v>18.687000000000001</v>
+      </c>
+      <c r="J37" s="14">
+        <f t="shared" si="2"/>
+        <v>2.6279999999999997</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A38" s="1">
         <v>1998</v>
       </c>
@@ -2769,8 +3261,21 @@
         <f t="shared" si="1"/>
         <v>310.37</v>
       </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G38" s="5">
+        <v>18.503</v>
+      </c>
+      <c r="H38" s="5">
+        <v>2.7</v>
+      </c>
+      <c r="I38" s="5">
+        <v>19.279</v>
+      </c>
+      <c r="J38" s="14">
+        <f t="shared" si="2"/>
+        <v>3.476</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A39" s="1">
         <v>1999</v>
       </c>
@@ -2791,8 +3296,21 @@
         <f t="shared" si="1"/>
         <v>355.41</v>
       </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G39" s="5">
+        <v>17.952999999999999</v>
+      </c>
+      <c r="H39" s="5">
+        <v>2.4239999999999999</v>
+      </c>
+      <c r="I39" s="5">
+        <v>19.277999999999999</v>
+      </c>
+      <c r="J39" s="14">
+        <f t="shared" si="2"/>
+        <v>3.7489999999999992</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A40" s="1">
         <v>2000</v>
       </c>
@@ -2813,8 +3331,21 @@
         <f t="shared" si="1"/>
         <v>459.14100000000002</v>
       </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G40" s="5">
+        <v>17.681999999999999</v>
+      </c>
+      <c r="H40" s="5">
+        <v>2.2040000000000002</v>
+      </c>
+      <c r="I40" s="5">
+        <v>20.018000000000001</v>
+      </c>
+      <c r="J40" s="14">
+        <f t="shared" si="2"/>
+        <v>4.5400000000000027</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A41" s="1">
         <v>2001</v>
       </c>
@@ -2835,8 +3366,21 @@
         <f t="shared" si="1"/>
         <v>334.43599999999998</v>
       </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G41" s="5">
+        <v>17.698</v>
+      </c>
+      <c r="H41" s="5">
+        <v>1.9590000000000001</v>
+      </c>
+      <c r="I41" s="5">
+        <v>18.916</v>
+      </c>
+      <c r="J41" s="14">
+        <f t="shared" si="2"/>
+        <v>3.177</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A42" s="1">
         <v>2002</v>
       </c>
@@ -2857,8 +3401,21 @@
         <f t="shared" si="1"/>
         <v>13.141999999999996</v>
       </c>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G42" s="5">
+        <v>18.57</v>
+      </c>
+      <c r="H42" s="5">
+        <v>1.579</v>
+      </c>
+      <c r="I42" s="5">
+        <v>17.113</v>
+      </c>
+      <c r="J42" s="14">
+        <f t="shared" si="2"/>
+        <v>0.12199999999999922</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A43" s="1">
         <v>2003</v>
       </c>
@@ -2879,8 +3436,21 @@
         <f t="shared" si="1"/>
         <v>-224.48499999999999</v>
       </c>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G43" s="5">
+        <v>19.149999999999999</v>
+      </c>
+      <c r="H43" s="5">
+        <v>1.357</v>
+      </c>
+      <c r="I43" s="5">
+        <v>15.802</v>
+      </c>
+      <c r="J43" s="14">
+        <f t="shared" si="2"/>
+        <v>-1.990999999999999</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A44" s="1">
         <v>2004</v>
       </c>
@@ -2901,8 +3471,21 @@
         <f t="shared" si="1"/>
         <v>-252.52699999999999</v>
       </c>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G44" s="5">
+        <v>19.062000000000001</v>
+      </c>
+      <c r="H44" s="5">
+        <v>1.3320000000000001</v>
+      </c>
+      <c r="I44" s="5">
+        <v>15.631</v>
+      </c>
+      <c r="J44" s="14">
+        <f t="shared" si="2"/>
+        <v>-2.0990000000000011</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A45" s="1">
         <v>2005</v>
       </c>
@@ -2923,8 +3506,21 @@
         <f t="shared" si="1"/>
         <v>-134.346</v>
       </c>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G45" s="5">
+        <v>19.251999999999999</v>
+      </c>
+      <c r="H45" s="5">
+        <v>1.4330000000000001</v>
+      </c>
+      <c r="I45" s="5">
+        <v>16.773</v>
+      </c>
+      <c r="J45" s="14">
+        <f t="shared" si="2"/>
+        <v>-1.0459999999999992</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A46" s="1">
         <v>2006</v>
       </c>
@@ -2945,8 +3541,21 @@
         <f t="shared" si="1"/>
         <v>-21.581000000000017</v>
       </c>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G46" s="5">
+        <v>19.47</v>
+      </c>
+      <c r="H46" s="5">
+        <v>1.6619999999999999</v>
+      </c>
+      <c r="I46" s="5">
+        <v>17.649999999999999</v>
+      </c>
+      <c r="J46" s="14">
+        <f t="shared" si="2"/>
+        <v>-0.15800000000000036</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A47" s="1">
         <v>2007</v>
       </c>
@@ -2967,8 +3576,21 @@
         <f t="shared" si="1"/>
         <v>76.399000000000001</v>
       </c>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G47" s="5">
+        <v>19.074999999999999</v>
+      </c>
+      <c r="H47" s="5">
+        <v>1.657</v>
+      </c>
+      <c r="I47" s="5">
+        <v>17.951000000000001</v>
+      </c>
+      <c r="J47" s="14">
+        <f t="shared" si="2"/>
+        <v>0.53300000000000125</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A48" s="1">
         <v>2008</v>
       </c>
@@ -2989,8 +3611,21 @@
         <f t="shared" si="1"/>
         <v>-205.75299999999999</v>
       </c>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G48" s="5">
+        <v>20.157</v>
+      </c>
+      <c r="H48" s="5">
+        <v>1.708</v>
+      </c>
+      <c r="I48" s="5">
+        <v>17.058</v>
+      </c>
+      <c r="J48" s="14">
+        <f t="shared" si="2"/>
+        <v>-1.3910000000000002</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A49" s="1">
         <v>2009</v>
       </c>
@@ -3011,8 +3646,21 @@
         <f t="shared" si="1"/>
         <v>-1225.788</v>
       </c>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G49" s="5">
+        <v>24.315000000000001</v>
+      </c>
+      <c r="H49" s="5">
+        <v>1.292</v>
+      </c>
+      <c r="I49" s="5">
+        <v>14.55</v>
+      </c>
+      <c r="J49" s="14">
+        <f t="shared" si="2"/>
+        <v>-8.4730000000000008</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A50" s="1">
         <v>2010</v>
       </c>
@@ -3033,8 +3681,21 @@
         <f t="shared" si="1"/>
         <v>-1098.173</v>
       </c>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G50" s="5">
+        <v>23.225999999999999</v>
+      </c>
+      <c r="H50" s="5">
+        <v>1.3180000000000001</v>
+      </c>
+      <c r="I50" s="5">
+        <v>14.53</v>
+      </c>
+      <c r="J50" s="14">
+        <f t="shared" si="2"/>
+        <v>-7.3780000000000001</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A51" s="1">
         <v>2011</v>
       </c>
@@ -3055,8 +3716,21 @@
         <f t="shared" si="1"/>
         <v>-1069.5989999999999</v>
       </c>
-    </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G51" s="5">
+        <v>23.295999999999999</v>
+      </c>
+      <c r="H51" s="5">
+        <v>1.4870000000000001</v>
+      </c>
+      <c r="I51" s="5">
+        <v>14.893000000000001</v>
+      </c>
+      <c r="J51" s="14">
+        <f t="shared" si="2"/>
+        <v>-6.9159999999999986</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A52" s="1">
         <v>2012</v>
       </c>
@@ -3077,8 +3751,21 @@
         <f t="shared" si="1"/>
         <v>-856.17300000000012</v>
       </c>
-    </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G52" s="5">
+        <v>21.890999999999998</v>
+      </c>
+      <c r="H52" s="5">
+        <v>1.3680000000000001</v>
+      </c>
+      <c r="I52" s="5">
+        <v>15.208</v>
+      </c>
+      <c r="J52" s="14">
+        <f t="shared" si="2"/>
+        <v>-5.3149999999999977</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A53" s="1">
         <v>2013</v>
       </c>
@@ -3099,8 +3786,21 @@
         <f t="shared" si="1"/>
         <v>-458.875</v>
       </c>
-    </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G53" s="5">
+        <v>20.702999999999999</v>
+      </c>
+      <c r="H53" s="5">
+        <v>1.3240000000000001</v>
+      </c>
+      <c r="I53" s="5">
+        <v>16.63</v>
+      </c>
+      <c r="J53" s="14">
+        <f t="shared" si="2"/>
+        <v>-2.7490000000000006</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A54" s="1">
         <v>2014</v>
       </c>
@@ -3121,8 +3821,21 @@
         <f t="shared" si="1"/>
         <v>-255.79300000000001</v>
       </c>
-    </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G54" s="5">
+        <v>20.119</v>
+      </c>
+      <c r="H54" s="5">
+        <v>1.3140000000000001</v>
+      </c>
+      <c r="I54" s="5">
+        <v>17.337</v>
+      </c>
+      <c r="J54" s="14">
+        <f t="shared" si="2"/>
+        <v>-1.468</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A55" s="1">
         <v>2015</v>
       </c>
@@ -3143,8 +3856,21 @@
         <f t="shared" si="1"/>
         <v>-218.76</v>
       </c>
-    </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G55" s="5">
+        <v>20.324999999999999</v>
+      </c>
+      <c r="H55" s="5">
+        <v>1.2290000000000001</v>
+      </c>
+      <c r="I55" s="5">
+        <v>17.891999999999999</v>
+      </c>
+      <c r="J55" s="14">
+        <f t="shared" si="2"/>
+        <v>-1.2039999999999997</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A56" s="1">
         <v>2016</v>
       </c>
@@ -3165,8 +3891,21 @@
         <f t="shared" si="1"/>
         <v>-344.65</v>
       </c>
-    </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G56" s="5">
+        <v>20.667000000000002</v>
+      </c>
+      <c r="H56" s="5">
+        <v>1.288</v>
+      </c>
+      <c r="I56" s="5">
+        <v>17.530999999999999</v>
+      </c>
+      <c r="J56" s="14">
+        <f t="shared" si="2"/>
+        <v>-1.8480000000000028</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A57" s="1">
         <v>2017</v>
       </c>
@@ -3187,8 +3926,21 @@
         <f t="shared" si="1"/>
         <v>-402.85</v>
       </c>
-    </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G57" s="5">
+        <v>20.55</v>
+      </c>
+      <c r="H57" s="5">
+        <v>1.355</v>
+      </c>
+      <c r="I57" s="5">
+        <v>17.116</v>
+      </c>
+      <c r="J57" s="14">
+        <f t="shared" si="2"/>
+        <v>-2.0790000000000011</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A58" s="1">
         <v>2018</v>
       </c>
@@ -3209,8 +3961,21 @@
         <f t="shared" si="1"/>
         <v>-454.07399999999996</v>
       </c>
-    </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G58" s="5">
+        <v>20.106000000000002</v>
+      </c>
+      <c r="H58" s="5">
+        <v>1.59</v>
+      </c>
+      <c r="I58" s="5">
+        <v>16.294</v>
+      </c>
+      <c r="J58" s="14">
+        <f t="shared" si="2"/>
+        <v>-2.2220000000000013</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A59" s="1">
         <v>2019</v>
       </c>
@@ -3231,8 +3996,21 @@
         <f t="shared" si="1"/>
         <v>-608.38799999999992</v>
       </c>
-    </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G59" s="5">
+        <v>20.890999999999998</v>
+      </c>
+      <c r="H59" s="5">
+        <v>1.762</v>
+      </c>
+      <c r="I59" s="5">
+        <v>16.271000000000001</v>
+      </c>
+      <c r="J59" s="14">
+        <f t="shared" si="2"/>
+        <v>-2.8579999999999974</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A60" s="1">
         <v>2020</v>
       </c>
@@ -3253,8 +4031,21 @@
         <f t="shared" si="1"/>
         <v>-2786.9560000000001</v>
       </c>
-    </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G60" s="5">
+        <v>30.739000000000001</v>
+      </c>
+      <c r="H60" s="5">
+        <v>1.62</v>
+      </c>
+      <c r="I60" s="5">
+        <v>16.047000000000001</v>
+      </c>
+      <c r="J60" s="14">
+        <f t="shared" si="2"/>
+        <v>-13.071999999999999</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A61" s="1">
         <v>2021</v>
       </c>
@@ -3275,8 +4066,21 @@
         <f t="shared" si="1"/>
         <v>-2423.0499999999997</v>
       </c>
-    </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G61" s="5">
+        <v>29.658000000000001</v>
+      </c>
+      <c r="H61" s="5">
+        <v>1.532</v>
+      </c>
+      <c r="I61" s="5">
+        <v>17.593</v>
+      </c>
+      <c r="J61" s="14">
+        <f t="shared" si="2"/>
+        <v>-10.533000000000001</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A62" s="1">
         <v>2022</v>
       </c>
@@ -3297,8 +4101,21 @@
         <f t="shared" si="1"/>
         <v>-899.95999999999992</v>
       </c>
-    </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G62" s="5">
+        <v>24.584</v>
+      </c>
+      <c r="H62" s="5">
+        <v>1.865</v>
+      </c>
+      <c r="I62" s="5">
+        <v>19.192</v>
+      </c>
+      <c r="J62" s="14">
+        <f t="shared" si="2"/>
+        <v>-3.5269999999999992</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A63" s="1">
         <v>2023</v>
       </c>
@@ -3319,8 +4136,21 @@
         <f t="shared" si="1"/>
         <v>-1035.425</v>
       </c>
-    </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G63" s="5">
+        <v>22.446999999999999</v>
+      </c>
+      <c r="H63" s="5">
+        <v>2.4089999999999998</v>
+      </c>
+      <c r="I63" s="5">
+        <v>16.248999999999999</v>
+      </c>
+      <c r="J63" s="14">
+        <f t="shared" si="2"/>
+        <v>-3.7890000000000006</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A64" s="1">
         <v>2024</v>
       </c>
@@ -3340,6 +4170,19 @@
       <c r="F64" s="14">
         <f t="shared" si="1"/>
         <v>-951.28100000000006</v>
+      </c>
+      <c r="G64" s="5">
+        <v>23.416</v>
+      </c>
+      <c r="H64" s="5">
+        <v>3.056</v>
+      </c>
+      <c r="I64" s="5">
+        <v>17.059999999999999</v>
+      </c>
+      <c r="J64" s="14">
+        <f t="shared" si="2"/>
+        <v>-3.3000000000000016</v>
       </c>
     </row>
   </sheetData>
